--- a/tests/fixtures/15_annual_budget/15_annual_budget_pattern-from-draft.xlsx
+++ b/tests/fixtures/15_annual_budget/15_annual_budget_pattern-from-draft.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q71"/>
+  <dimension ref="A1:Q72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="10" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -471,70 +471,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>config:</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>pattern.version</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>config:</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>read.direction</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>LR</t>
         </is>
       </c>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
-      <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="n"/>
-      <c r="I1" s="1" t="n"/>
-      <c r="J1" s="1" t="n"/>
-      <c r="K1" s="1" t="n"/>
-      <c r="L1" s="1" t="n"/>
-      <c r="M1" s="1" t="n"/>
-      <c r="N1" s="1" t="n"/>
-      <c r="O1" s="1" t="n"/>
-      <c r="P1" s="1" t="n"/>
-      <c r="Q1" s="1" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>lbl:</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>lbl_income</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Total monthly income</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="n"/>
-      <c r="J2" s="2" t="n"/>
-      <c r="K2" s="2" t="n"/>
-      <c r="L2" s="2" t="n"/>
-      <c r="M2" s="2" t="n"/>
-      <c r="N2" s="2" t="n"/>
-      <c r="O2" s="2" t="n"/>
-      <c r="P2" s="2" t="n"/>
-      <c r="Q2" s="2" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
+      <c r="I2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
+      <c r="K2" s="1" t="n"/>
+      <c r="L2" s="1" t="n"/>
+      <c r="M2" s="1" t="n"/>
+      <c r="N2" s="1" t="n"/>
+      <c r="O2" s="1" t="n"/>
+      <c r="P2" s="1" t="n"/>
+      <c r="Q2" s="1" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -544,7 +526,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>lbl_expenses_s</t>
+          <t>lbl_income</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -554,7 +536,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Total monthly expenses</t>
+          <t>Total monthly income</t>
         </is>
       </c>
       <c r="E3" s="2" t="n"/>
@@ -579,7 +561,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>col_item</t>
+          <t>lbl_expenses_s</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -589,7 +571,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>Total monthly expenses</t>
         </is>
       </c>
       <c r="E4" s="2" t="n"/>
@@ -614,7 +596,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>col_jan</t>
+          <t>col_item</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -624,7 +606,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="E5" s="2" t="n"/>
@@ -649,7 +631,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>col_feb</t>
+          <t>col_jan</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -659,7 +641,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="E6" s="2" t="n"/>
@@ -684,7 +666,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>col_mar</t>
+          <t>col_feb</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -694,7 +676,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="E7" s="2" t="n"/>
@@ -719,7 +701,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>col_apr</t>
+          <t>col_mar</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -729,7 +711,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="E8" s="2" t="n"/>
@@ -754,7 +736,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>col_may</t>
+          <t>col_apr</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -764,7 +746,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="E9" s="2" t="n"/>
@@ -789,7 +771,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>col_jun</t>
+          <t>col_may</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -799,7 +781,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>May</t>
         </is>
       </c>
       <c r="E10" s="2" t="n"/>
@@ -824,7 +806,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>col_jul</t>
+          <t>col_jun</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -834,7 +816,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Jul</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="E11" s="2" t="n"/>
@@ -859,7 +841,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>col_aug</t>
+          <t>col_jul</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -869,7 +851,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Jul</t>
         </is>
       </c>
       <c r="E12" s="2" t="n"/>
@@ -894,7 +876,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>col_sep</t>
+          <t>col_aug</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -904,7 +886,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>Aug</t>
         </is>
       </c>
       <c r="E13" s="2" t="n"/>
@@ -929,7 +911,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>col_oct</t>
+          <t>col_sep</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -939,7 +921,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="E14" s="2" t="n"/>
@@ -964,7 +946,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>col_nov</t>
+          <t>col_oct</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -974,7 +956,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="E15" s="2" t="n"/>
@@ -999,7 +981,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>col_dec</t>
+          <t>col_nov</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1009,7 +991,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="E16" s="2" t="n"/>
@@ -1034,7 +1016,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>col_total_hdr</t>
+          <t>col_dec</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1044,7 +1026,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="E17" s="2" t="n"/>
@@ -1069,7 +1051,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>col_avg_hdr</t>
+          <t>col_total_hdr</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1079,7 +1061,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E18" s="2" t="n"/>
@@ -1097,39 +1079,39 @@
       <c r="Q18" s="2" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>var:</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>summary.income</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>.*</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n"/>
-      <c r="G19" s="3" t="n"/>
-      <c r="H19" s="3" t="n"/>
-      <c r="I19" s="3" t="n"/>
-      <c r="J19" s="3" t="n"/>
-      <c r="K19" s="3" t="n"/>
-      <c r="L19" s="3" t="n"/>
-      <c r="M19" s="3" t="n"/>
-      <c r="N19" s="3" t="n"/>
-      <c r="O19" s="3" t="n"/>
-      <c r="P19" s="3" t="n"/>
-      <c r="Q19" s="3" t="n"/>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>lbl:</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>col_avg_hdr</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n"/>
+      <c r="F19" s="2" t="n"/>
+      <c r="G19" s="2" t="n"/>
+      <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="n"/>
+      <c r="K19" s="2" t="n"/>
+      <c r="L19" s="2" t="n"/>
+      <c r="M19" s="2" t="n"/>
+      <c r="N19" s="2" t="n"/>
+      <c r="O19" s="2" t="n"/>
+      <c r="P19" s="2" t="n"/>
+      <c r="Q19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -1139,7 +1121,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>summary.expenses</t>
+          <t>summary.income</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -1174,7 +1156,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>summary.balance</t>
+          <t>summary.expenses</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -1209,12 +1191,12 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>summary.pct_spent</t>
+          <t>summary.balance</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>percentage</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -1244,17 +1226,17 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>transaction.item</t>
+          <t>summary.pct_spent</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>percentage</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>.+</t>
+          <t>.*</t>
         </is>
       </c>
       <c r="E23" s="3" t="n"/>
@@ -1279,17 +1261,17 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>transaction.jan</t>
+          <t>transaction.item</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>.*</t>
+          <t>.+</t>
         </is>
       </c>
       <c r="E24" s="3" t="n"/>
@@ -1314,7 +1296,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>transaction.feb</t>
+          <t>transaction.jan</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -1349,7 +1331,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>transaction.mar</t>
+          <t>transaction.feb</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -1384,7 +1366,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>transaction.apr</t>
+          <t>transaction.mar</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -1419,7 +1401,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>transaction.may</t>
+          <t>transaction.apr</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -1454,7 +1436,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>transaction.jun</t>
+          <t>transaction.may</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -1489,7 +1471,7 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>transaction.jul</t>
+          <t>transaction.jun</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -1524,7 +1506,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>transaction.aug</t>
+          <t>transaction.jul</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -1559,7 +1541,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>transaction.sep</t>
+          <t>transaction.aug</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -1594,7 +1576,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>transaction.oct</t>
+          <t>transaction.sep</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -1629,7 +1611,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>transaction.nov</t>
+          <t>transaction.oct</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -1664,7 +1646,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>transaction.dec</t>
+          <t>transaction.nov</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -1699,7 +1681,7 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>transaction.total</t>
+          <t>transaction.dec</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -1734,7 +1716,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>transaction.avg</t>
+          <t>transaction.total</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -1769,17 +1751,17 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>transaction_total.label</t>
+          <t>transaction.avg</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>.*</t>
         </is>
       </c>
       <c r="E38" s="3" t="n"/>
@@ -1804,17 +1786,17 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>transaction_total.jan</t>
+          <t>transaction_total.label</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>.*</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E39" s="3" t="n"/>
@@ -1839,7 +1821,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>transaction_total.feb</t>
+          <t>transaction_total.jan</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -1874,7 +1856,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>transaction_total.mar</t>
+          <t>transaction_total.feb</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -1909,7 +1891,7 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>transaction_total.apr</t>
+          <t>transaction_total.mar</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -1944,7 +1926,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>transaction_total.may</t>
+          <t>transaction_total.apr</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -1979,7 +1961,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>transaction_total.jun</t>
+          <t>transaction_total.may</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -2014,7 +1996,7 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>transaction_total.jul</t>
+          <t>transaction_total.jun</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -2049,7 +2031,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>transaction_total.aug</t>
+          <t>transaction_total.jul</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -2084,7 +2066,7 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>transaction_total.sep</t>
+          <t>transaction_total.aug</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -2119,7 +2101,7 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>transaction_total.oct</t>
+          <t>transaction_total.sep</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -2154,7 +2136,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>transaction_total.nov</t>
+          <t>transaction_total.oct</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -2189,7 +2171,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>transaction_total.dec</t>
+          <t>transaction_total.nov</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -2224,7 +2206,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>transaction_total.annual</t>
+          <t>transaction_total.dec</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -2259,7 +2241,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>transaction_total.avg</t>
+          <t>transaction_total.annual</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -2294,17 +2276,17 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>header.title</t>
+          <t>transaction_total.avg</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>.+</t>
+          <t>.*</t>
         </is>
       </c>
       <c r="E53" s="3" t="n"/>
@@ -2322,59 +2304,67 @@
       <c r="Q53" s="3" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>header.title</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>.+</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="n"/>
+      <c r="F54" s="3" t="n"/>
+      <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
+      <c r="I54" s="3" t="n"/>
+      <c r="J54" s="3" t="n"/>
+      <c r="K54" s="3" t="n"/>
+      <c r="L54" s="3" t="n"/>
+      <c r="M54" s="3" t="n"/>
+      <c r="N54" s="3" t="n"/>
+      <c r="O54" s="3" t="n"/>
+      <c r="P54" s="3" t="n"/>
+      <c r="Q54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>START:</t>
         </is>
       </c>
-      <c r="B54" s="4" t="n"/>
-      <c r="C54" s="4" t="n"/>
-      <c r="D54" s="4" t="n"/>
-      <c r="E54" s="4" t="n"/>
-      <c r="F54" s="4" t="n"/>
-      <c r="G54" s="4" t="n"/>
-      <c r="H54" s="4" t="n"/>
-      <c r="I54" s="4" t="n"/>
-      <c r="J54" s="4" t="n"/>
-      <c r="K54" s="4" t="n"/>
-      <c r="L54" s="4" t="n"/>
-      <c r="M54" s="4" t="n"/>
-      <c r="N54" s="4" t="n"/>
-      <c r="O54" s="4" t="n"/>
-      <c r="P54" s="4" t="n"/>
-      <c r="Q54" s="4" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>cell:B2</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>IGNORE</t>
-        </is>
-      </c>
-      <c r="C55" s="5" t="n"/>
-      <c r="D55" s="5" t="n"/>
-      <c r="E55" s="5" t="n"/>
-      <c r="F55" s="5" t="n"/>
-      <c r="G55" s="5" t="n"/>
-      <c r="H55" s="5" t="n"/>
-      <c r="I55" s="5" t="n"/>
-      <c r="J55" s="5" t="n"/>
-      <c r="K55" s="5" t="n"/>
-      <c r="L55" s="5" t="n"/>
-      <c r="M55" s="5" t="n"/>
-      <c r="N55" s="5" t="n"/>
-      <c r="O55" s="5" t="n"/>
-      <c r="P55" s="5" t="n"/>
-      <c r="Q55" s="5" t="n"/>
+      <c r="B55" s="4" t="n"/>
+      <c r="C55" s="4" t="n"/>
+      <c r="D55" s="4" t="n"/>
+      <c r="E55" s="4" t="n"/>
+      <c r="F55" s="4" t="n"/>
+      <c r="G55" s="4" t="n"/>
+      <c r="H55" s="4" t="n"/>
+      <c r="I55" s="4" t="n"/>
+      <c r="J55" s="4" t="n"/>
+      <c r="K55" s="4" t="n"/>
+      <c r="L55" s="4" t="n"/>
+      <c r="M55" s="4" t="n"/>
+      <c r="N55" s="4" t="n"/>
+      <c r="O55" s="4" t="n"/>
+      <c r="P55" s="4" t="n"/>
+      <c r="Q55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>cell:B4</t>
+          <t>cell:B2</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
@@ -2401,12 +2391,12 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>cell:B5</t>
+          <t>cell:B4</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>lbl_income</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="C57" s="5" t="n"/>
@@ -2428,12 +2418,12 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>cell:C5</t>
+          <t>cell:B5</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>summary.income</t>
+          <t>lbl_income</t>
         </is>
       </c>
       <c r="C58" s="5" t="n"/>
@@ -2455,12 +2445,12 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>cell:B6</t>
+          <t>cell:C5</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>lbl_expenses_s</t>
+          <t>summary.income</t>
         </is>
       </c>
       <c r="C59" s="5" t="n"/>
@@ -2482,12 +2472,12 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>cell:C6</t>
+          <t>cell:B6</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>summary.expenses</t>
+          <t>lbl_expenses_s</t>
         </is>
       </c>
       <c r="C60" s="5" t="n"/>
@@ -2509,12 +2499,12 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>cell:B8</t>
+          <t>cell:C6</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>IGNORE</t>
+          <t>summary.expenses</t>
         </is>
       </c>
       <c r="C61" s="5" t="n"/>
@@ -2536,12 +2526,12 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>cell:C8</t>
+          <t>cell:B8</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>summary.balance</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="C62" s="5" t="n"/>
@@ -2563,12 +2553,12 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>cell:B10</t>
+          <t>cell:C8</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>IGNORE</t>
+          <t>summary.balance</t>
         </is>
       </c>
       <c r="C63" s="5" t="n"/>
@@ -2590,12 +2580,12 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>cell:C10</t>
+          <t>cell:B10</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>summary.pct_spent</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="C64" s="5" t="n"/>
@@ -2614,112 +2604,56 @@
       <c r="P64" s="5" t="n"/>
       <c r="Q64" s="5" t="n"/>
     </row>
-    <row r="65"/>
-    <row r="66">
-      <c r="A66" s="6" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>cell:C10</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>summary.pct_spent</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="n"/>
+      <c r="D65" s="5" t="n"/>
+      <c r="E65" s="5" t="n"/>
+      <c r="F65" s="5" t="n"/>
+      <c r="G65" s="5" t="n"/>
+      <c r="H65" s="5" t="n"/>
+      <c r="I65" s="5" t="n"/>
+      <c r="J65" s="5" t="n"/>
+      <c r="K65" s="5" t="n"/>
+      <c r="L65" s="5" t="n"/>
+      <c r="M65" s="5" t="n"/>
+      <c r="N65" s="5" t="n"/>
+      <c r="O65" s="5" t="n"/>
+      <c r="P65" s="5" t="n"/>
+      <c r="Q65" s="5" t="n"/>
+    </row>
+    <row r="66"/>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
         <is>
           <t>table:*</t>
         </is>
       </c>
-      <c r="B66" s="6" t="n"/>
-      <c r="C66" s="6" t="n"/>
-      <c r="D66" s="6" t="n"/>
-      <c r="E66" s="6" t="n"/>
-      <c r="F66" s="6" t="n"/>
-      <c r="G66" s="6" t="n"/>
-      <c r="H66" s="6" t="n"/>
-      <c r="I66" s="6" t="n"/>
-      <c r="J66" s="6" t="n"/>
-      <c r="K66" s="6" t="n"/>
-      <c r="L66" s="6" t="n"/>
-      <c r="M66" s="6" t="n"/>
-      <c r="N66" s="6" t="n"/>
-      <c r="O66" s="6" t="n"/>
-      <c r="P66" s="6" t="n"/>
-      <c r="Q66" s="6" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="n"/>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>HEADER:1</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>header.title</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="K67" s="2" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="N67" s="2" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="O67" s="2" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="P67" s="2" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="Q67" s="2" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
+      <c r="B67" s="6" t="n"/>
+      <c r="C67" s="6" t="n"/>
+      <c r="D67" s="6" t="n"/>
+      <c r="E67" s="6" t="n"/>
+      <c r="F67" s="6" t="n"/>
+      <c r="G67" s="6" t="n"/>
+      <c r="H67" s="6" t="n"/>
+      <c r="I67" s="6" t="n"/>
+      <c r="J67" s="6" t="n"/>
+      <c r="K67" s="6" t="n"/>
+      <c r="L67" s="6" t="n"/>
+      <c r="M67" s="6" t="n"/>
+      <c r="N67" s="6" t="n"/>
+      <c r="O67" s="6" t="n"/>
+      <c r="P67" s="6" t="n"/>
+      <c r="Q67" s="6" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n"/>
@@ -2730,268 +2664,351 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
+          <t>header.title</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>HEADER:1</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
           <t>col_item</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>col_jan</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>col_feb</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>col_mar</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>col_apr</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>col_may</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr">
+      <c r="I69" s="2" t="inlineStr">
         <is>
           <t>col_jun</t>
         </is>
       </c>
-      <c r="J68" s="2" t="inlineStr">
+      <c r="J69" s="2" t="inlineStr">
         <is>
           <t>col_jul</t>
         </is>
       </c>
-      <c r="K68" s="2" t="inlineStr">
+      <c r="K69" s="2" t="inlineStr">
         <is>
           <t>col_aug</t>
         </is>
       </c>
-      <c r="L68" s="2" t="inlineStr">
+      <c r="L69" s="2" t="inlineStr">
         <is>
           <t>col_sep</t>
         </is>
       </c>
-      <c r="M68" s="2" t="inlineStr">
+      <c r="M69" s="2" t="inlineStr">
         <is>
           <t>col_oct</t>
         </is>
       </c>
-      <c r="N68" s="2" t="inlineStr">
+      <c r="N69" s="2" t="inlineStr">
         <is>
           <t>col_nov</t>
         </is>
       </c>
-      <c r="O68" s="2" t="inlineStr">
+      <c r="O69" s="2" t="inlineStr">
         <is>
           <t>col_dec</t>
         </is>
       </c>
-      <c r="P68" s="2" t="inlineStr">
+      <c r="P69" s="2" t="inlineStr">
         <is>
           <t>col_total_hdr</t>
         </is>
       </c>
-      <c r="Q68" s="2" t="inlineStr">
+      <c r="Q69" s="2" t="inlineStr">
         <is>
           <t>col_avg_hdr</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="3" t="n"/>
-      <c r="B69" s="3" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="3" t="n"/>
+      <c r="B70" s="3" t="inlineStr">
         <is>
           <t>DATA:*</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>transaction.item</t>
         </is>
       </c>
-      <c r="D69" s="3" t="inlineStr">
+      <c r="D70" s="3" t="inlineStr">
         <is>
           <t>transaction.jan</t>
         </is>
       </c>
-      <c r="E69" s="3" t="inlineStr">
+      <c r="E70" s="3" t="inlineStr">
         <is>
           <t>transaction.feb</t>
         </is>
       </c>
-      <c r="F69" s="3" t="inlineStr">
+      <c r="F70" s="3" t="inlineStr">
         <is>
           <t>transaction.mar</t>
         </is>
       </c>
-      <c r="G69" s="3" t="inlineStr">
+      <c r="G70" s="3" t="inlineStr">
         <is>
           <t>transaction.apr</t>
         </is>
       </c>
-      <c r="H69" s="3" t="inlineStr">
+      <c r="H70" s="3" t="inlineStr">
         <is>
           <t>transaction.may</t>
         </is>
       </c>
-      <c r="I69" s="3" t="inlineStr">
+      <c r="I70" s="3" t="inlineStr">
         <is>
           <t>transaction.jun</t>
         </is>
       </c>
-      <c r="J69" s="3" t="inlineStr">
+      <c r="J70" s="3" t="inlineStr">
         <is>
           <t>transaction.jul</t>
         </is>
       </c>
-      <c r="K69" s="3" t="inlineStr">
+      <c r="K70" s="3" t="inlineStr">
         <is>
           <t>transaction.aug</t>
         </is>
       </c>
-      <c r="L69" s="3" t="inlineStr">
+      <c r="L70" s="3" t="inlineStr">
         <is>
           <t>transaction.sep</t>
         </is>
       </c>
-      <c r="M69" s="3" t="inlineStr">
+      <c r="M70" s="3" t="inlineStr">
         <is>
           <t>transaction.oct</t>
         </is>
       </c>
-      <c r="N69" s="3" t="inlineStr">
+      <c r="N70" s="3" t="inlineStr">
         <is>
           <t>transaction.nov</t>
         </is>
       </c>
-      <c r="O69" s="3" t="inlineStr">
+      <c r="O70" s="3" t="inlineStr">
         <is>
           <t>transaction.dec</t>
         </is>
       </c>
-      <c r="P69" s="3" t="inlineStr">
+      <c r="P70" s="3" t="inlineStr">
         <is>
           <t>transaction.total</t>
         </is>
       </c>
-      <c r="Q69" s="3" t="inlineStr">
+      <c r="Q70" s="3" t="inlineStr">
         <is>
           <t>transaction.avg</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="1" t="n"/>
-      <c r="B70" s="1" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="1" t="n"/>
+      <c r="B71" s="1" t="inlineStr">
         <is>
           <t>FOOTER:1</t>
         </is>
       </c>
-      <c r="C70" s="1" t="inlineStr">
+      <c r="C71" s="1" t="inlineStr">
         <is>
           <t>transaction_total.label</t>
         </is>
       </c>
-      <c r="D70" s="1" t="inlineStr">
+      <c r="D71" s="1" t="inlineStr">
         <is>
           <t>transaction_total.jan</t>
         </is>
       </c>
-      <c r="E70" s="1" t="inlineStr">
+      <c r="E71" s="1" t="inlineStr">
         <is>
           <t>transaction_total.feb</t>
         </is>
       </c>
-      <c r="F70" s="1" t="inlineStr">
+      <c r="F71" s="1" t="inlineStr">
         <is>
           <t>transaction_total.mar</t>
         </is>
       </c>
-      <c r="G70" s="1" t="inlineStr">
+      <c r="G71" s="1" t="inlineStr">
         <is>
           <t>transaction_total.apr</t>
         </is>
       </c>
-      <c r="H70" s="1" t="inlineStr">
+      <c r="H71" s="1" t="inlineStr">
         <is>
           <t>transaction_total.may</t>
         </is>
       </c>
-      <c r="I70" s="1" t="inlineStr">
+      <c r="I71" s="1" t="inlineStr">
         <is>
           <t>transaction_total.jun</t>
         </is>
       </c>
-      <c r="J70" s="1" t="inlineStr">
+      <c r="J71" s="1" t="inlineStr">
         <is>
           <t>transaction_total.jul</t>
         </is>
       </c>
-      <c r="K70" s="1" t="inlineStr">
+      <c r="K71" s="1" t="inlineStr">
         <is>
           <t>transaction_total.aug</t>
         </is>
       </c>
-      <c r="L70" s="1" t="inlineStr">
+      <c r="L71" s="1" t="inlineStr">
         <is>
           <t>transaction_total.sep</t>
         </is>
       </c>
-      <c r="M70" s="1" t="inlineStr">
+      <c r="M71" s="1" t="inlineStr">
         <is>
           <t>transaction_total.oct</t>
         </is>
       </c>
-      <c r="N70" s="1" t="inlineStr">
+      <c r="N71" s="1" t="inlineStr">
         <is>
           <t>transaction_total.nov</t>
         </is>
       </c>
-      <c r="O70" s="1" t="inlineStr">
+      <c r="O71" s="1" t="inlineStr">
         <is>
           <t>transaction_total.dec</t>
         </is>
       </c>
-      <c r="P70" s="1" t="inlineStr">
+      <c r="P71" s="1" t="inlineStr">
         <is>
           <t>transaction_total.annual</t>
         </is>
       </c>
-      <c r="Q70" s="1" t="inlineStr">
+      <c r="Q71" s="1" t="inlineStr">
         <is>
           <t>transaction_total.avg</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="4" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
         <is>
           <t>END:</t>
         </is>
       </c>
-      <c r="B71" s="4" t="n"/>
-      <c r="C71" s="4" t="n"/>
-      <c r="D71" s="4" t="n"/>
-      <c r="E71" s="4" t="n"/>
-      <c r="F71" s="4" t="n"/>
-      <c r="G71" s="4" t="n"/>
-      <c r="H71" s="4" t="n"/>
-      <c r="I71" s="4" t="n"/>
-      <c r="J71" s="4" t="n"/>
-      <c r="K71" s="4" t="n"/>
-      <c r="L71" s="4" t="n"/>
-      <c r="M71" s="4" t="n"/>
-      <c r="N71" s="4" t="n"/>
-      <c r="O71" s="4" t="n"/>
-      <c r="P71" s="4" t="n"/>
-      <c r="Q71" s="4" t="n"/>
+      <c r="B72" s="4" t="n"/>
+      <c r="C72" s="4" t="n"/>
+      <c r="D72" s="4" t="n"/>
+      <c r="E72" s="4" t="n"/>
+      <c r="F72" s="4" t="n"/>
+      <c r="G72" s="4" t="n"/>
+      <c r="H72" s="4" t="n"/>
+      <c r="I72" s="4" t="n"/>
+      <c r="J72" s="4" t="n"/>
+      <c r="K72" s="4" t="n"/>
+      <c r="L72" s="4" t="n"/>
+      <c r="M72" s="4" t="n"/>
+      <c r="N72" s="4" t="n"/>
+      <c r="O72" s="4" t="n"/>
+      <c r="P72" s="4" t="n"/>
+      <c r="Q72" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
